--- a/data_extactor/batch_10_fa/batch_0025_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0025_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Assessment Systems Corporation XCALIBRE | Google Sheets | نرم‌افزار اطلاعات منابع انسانی HRIS | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Statistics | سیستم مدیریت یادگیری LMS | Mentimeter | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Word | Muthen &amp; Muthen Mplus | Oracle PeopleSoft | Padlet | نرم‌افزار آزمون روان‌سنجی | SAS | Scientific Software International BILOG-MG | Scientific Software International HLM | Scientific Software International LISREL | Scientific Software International MULTILOG | Scientific Software International PARSCALE | Scientific Software International TESTFACT | نرم‌افزار مرورگر وب | Winsteps</t>
+          <t>Adobe Acrobat | Assessment Systems Corporation XCALIBRE | Google Sheets | سیستم اطلاعات منابع انسانی (HRIS) | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Statistics | سیستم مدیریت یادگیری LMS | Mentimeter | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Word | Muthen &amp; Muthen Mplus | Oracle PeopleSoft | Padlet | نرم‌افزار آزمون روان‌سنجی | SAS | Scientific Software International BILOG-MG | Scientific Software International HLM | Scientific Software International LISREL | Scientific Software International MULTILOG | Scientific Software International PARSCALE | Scientific Software International TESTFACT | نرم‌افزار مرورگر وب | Winsteps</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نوشتن | صحبت کردن | تفکر انتقادی | یادگیری فعال | نظارت | علم | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پرسنل و منابع انسانی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره | ریاضیات | زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | کامپیوتر و الکترونیک | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>پرسنل و منابع انسانی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره | ریاضیات | زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک نوشتاری | بیان نوشتاری | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | نظم‌دهی اطلاعات | روانی ایده‌ها | اصالت | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | دید نزدیک | توجه انتخابی | توانایی عددی | دید دور</t>
+          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | توانایی عددی | بینایی دور</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | تکرار تصمیم‌گیری | نتایج کاری و خروجی‌های سایر کارکنان</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>معلمان کسب‌وکار، پس از متوسطه | روان‌شناسان بالینی و مشاوره | دانشمندان داده | مدیران آموزشی، پس از متوسطه | معلمان آموزشی، پس از متوسطه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | دستیاران منابع انسانی، به جز حقوق و دستمزد و زمان‌سنجی | مدیران منابع انسانی | متخصصان منابع انسانی | هماهنگ‌کنندگان آموزشی | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | متخصصان مدیریت پروژه | معلمان روان‌شناسی، پس از متوسطه | مشاوران توان‌بخشی | روان‌شناسان مدرسه | معلمان مددکاری اجتماعی، پس از متوسطه | مدیران خدمات اجتماعی و جامعه | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
+          <t>اساتید کسب‌وکار، پس از متوسطه | روان‌شناسان بالینی و مشاوره | دانشمندان داده | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | مدیران منابع انسانی | متخصصان منابع انسانی | هماهنگ‌کنندگان آموزشی | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | متخصصان مدیریت پروژه | استادان روان‌شناسی، پس از متوسطه | مشاوران توانبخشی | روان‌شناسان مدرسه | مدرسان مددکاری اجتماعی، آموزش عالی | مدیران خدمات اجتماعی و جامعه | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Addison Health Systems WritePad EHR | Anasazi Software Client Data System | Athena Software Penelope Case Management | B Sharp Technologies B Care | BRB Software HorizonMIS | BlackHawk Canyon Publishers PracticianWorks | Blueberry Harbor Software Clinical Record Keeper | Bluewater Management Systems BMCASE | Clinivate Clinitrak | Comprehensive Affect Testing System CATS | Core Solutions Care Enterprise | DocuTrac QuicDoc | Fagerman Technologies MedLook | Google Docs | Google Meet | Google Sheets | Health Care Software HCS INTERACTANT | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | ICANotes | JTL Enterprises MedIntake | MICA Information Systems MICA-MED Practice Manager | MPMsoft billing | MS*Health Software/CMHC | Mdansby The PsychReport | MedEZ behavioral healthcare and substance abuse software | Medical Outcome Systems eMINI Software Suite | Medicine Rules PowerSEAT 360 | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Teams | Microsoft Word | My Clients Plus | Neuro Innovations Therapist's Toolkit | Neurobehavioral Systems Presentation | Noldus Information Technology The Observer XT | O*NET OnLine | Office Management Systems Mental Health Office All-in-One | Polaris Health Directions Polaris-MH | Practice Management Technologies Visual Private Office | PsyTech Solutions Epitomax | PsychAssistant | PsychNotesEMR | Psyquel | Serenic Navigator CommunityCare | Sigmund Software Sigmund Enterprise Management | SpectraSoft AppointmentsPRO | نرم‌افزار آماری | نرم‌افزار آزمون | TheraManager | Thriveworks TherapyBuddy | Trinity Software Solutions BEACON | UNI/CARE Pro-Filer | نرم‌افزار مرورگر وب | Zoom | نرم‌افزار eClinicalWorks EHR</t>
+          <t>Addison Health Systems WritePad EHR | Anasazi Software Client Data System | مدیریت پرونده Athena Software Penelope | B Sharp Technologies B Care | BRB Software HorizonMIS | BlackHawk Canyon Publishers PracticianWorks | Blueberry Harbor Software Clinical Record Keeper | Bluewater Management Systems BMCASE | Clinivate Clinitrak | Comprehensive Affect Testing System CATS | Core Solutions Care Enterprise | DocuTrac QuicDoc | Fagerman Technologies MedLook | Google Docs | Google Meet | Google Sheets | Health Care Software HCS INTERACTANT | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | ICANotes | JTL Enterprises MedIntake | MICA Information Systems MICA-MED Practice Manager | MPMsoft billing | MS*Health Software/CMHC | Mdansby The PsychReport | MedEZ behavioral healthcare and substance abuse software | Medical Outcome Systems eMINI Software Suite | Medicine Rules PowerSEAT 360 | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Teams | Microsoft Word | My Clients Plus | Neuro Innovations Therapist's Toolkit | Neurobehavioral Systems Presentation | Noldus Information Technology The Observer XT | O*NET OnLine | Office Management Systems Mental Health Office All-in-One | Polaris Health Directions Polaris-MH | Practice Management Technologies Visual Private Office | PsyTech Solutions Epitomax | PsychAssistant | PsychNotesEMR | Psyquel | Serenic Navigator CommunityCare | Sigmund Software Sigmund Enterprise Management | SpectraSoft AppointmentsPRO | نرم‌افزار آماری | نرم‌افزار آزمون | TheraManager | Thriveworks TherapyBuddy | Trinity Software Solutions BEACON | UNI/CARE Pro-Filer | نرم‌افزار مرورگر وب | Zoom | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | نوشتن | تفکر انتقادی | گوش دادن فعال | صحبت کردن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک نوشتاری | درک شفاهی | حساسیت به مسئله | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | توجه انتخابی | دید نزدیک | انعطاف‌پذیری بستار</t>
+          <t>بیان شفاهی | درک کتبی | درک شفاهی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | توجه انتخابی | بینایی نزدیک | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ایمیل | تماس با دیگران | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | پیامد خطا | فشار زمانی | اهمیت دقیق یا صحیح بودن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ایمیل | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | پیامد خطا | فشار زمانی | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران روان‌پزشکی پیشرفته | مددکاران اجتماعی کودک، خانواده و مدرسه | عصب‌روان‌شناسان بالینی | پرستاران بالینی متخصص | پزشکان طب خانواده | مشاوران ژنتیک | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | عصب‌روان‌شناسان | کاردرمانگران | دستیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توان‌بخشی | روان‌شناسان مدرسه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>پرستاران پیشرفته روانپزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | عصب‌روان‌شناسان بالینی | متخصصان پرستاری بالینی | پزشکان خانواده | مشاوران ژنتیک | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | عصب‌روان‌شناسان | کاردرمانگران | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توانبخشی | روان‌شناسان مدرسه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | نظارت | تفکر انتقادی | نوشتن | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | آموزش و پرورش | جامعه‌شناسی و مردم‌شناسی | خدمات مشتری و شخصی | اداری | ریاضیات | قانون و دولت | کامپیوتر و الکترونیک | زبان انگلیسی</t>
+          <t>روان‌شناسی | درمان و مشاوره | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | اداری | ریاضیات | قانون و دولت | رایانه و الکترونیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک نوشتاری | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | وضوح گفتار | بیان نوشتاری | تشخیص گفتار | دید نزدیک | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | وضوح گفتار | بیان کتبی | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | فشار زمانی | صرف زمان برای نشستن | برخورد با مشتریان خارجی یا عموم مردم | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | مکالمات تلفنی | اهمیت دقیق یا درست بودن | فشار زمانی | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | عصب‌روان‌شناسان بالینی | روان‌شناسان بالینی و مشاوره | مدیران آموزشی، کودکستان تا متوسطه | معلمان آموزشی، پس از متوسطه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به جز آموزش ویژه | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | عصب‌روان‌شناسان | روان‌پزشکان | معلمان روان‌شناسی، پس از متوسطه | مشاوران توان‌بخشی | معلمان مددکاری اجتماعی، پس از متوسطه | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، دبیرستان | معلمان خصوصی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | عصب‌روان‌شناسان بالینی | روان‌شناسان بالینی و مشاوره | مدیران آموزشی، مهدکودک تا دبیرستان | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | عصب‌روان‌شناسان | روان‌پزشکان | استادان روان‌شناسی، پس از متوسطه | مشاوران توانبخشی | مدرسان مددکاری اجتماعی، آموزش عالی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | صحبت کردن | نوشتن | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>روان‌شناسی | زبان انگلیسی | درمان و مشاوره | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | ریاضیات | خدمات مشتری و شخصی | کامپیوتر و الکترونیک | مدیریت و اداره</t>
+          <t>روان‌شناسی | زبان انگلیسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | ریاضیات | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | اشتراک زمانی | تجسم | حافظه</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | سخنرانی عمومی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | سخنرانی عمومی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>روان‌شناسان بالینی و مشاوره | روان‌شناسان مدرسه | روان‌شناسان صنعتی-سازمانی | عصب‌روان‌شناسان | عصب‌روان‌شناسان بالینی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران سوءمصرف مواد و اختلالات رفتاری | مشاوران توان‌بخشی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | جامعه‌شناسان | پژوهشگران نظرسنجی | دستیاران پژوهشی علوم اجتماعی | معلمان روان‌شناسی، پس از متوسطه | مددکاران اجتماعی مراقبت‌های بهداشتی | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | دانشمندان پزشکی، به جز اپیدمیولوژیست‌ها | مردم‌شناسان و باستان‌شناسان | متخصصان منابع انسانی | متخصصان آموزش سلامت</t>
+          <t>روان‌شناسان بالینی و مشاوره | روان‌شناسان مدرسه | روان‌شناسان صنعتی-سازمانی | عصب‌روان‌شناسان | عصب‌روان‌شناسان بالینی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران سوءمصرف مواد و اختلالات رفتاری | مشاوران توانبخشی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | جامعه‌شناسان | پژوهشگران نظرسنجی | دستیاران تحقیقات علوم اجتماعی | استادان روان‌شناسی، پس از متوسطه | مددکاران اجتماعی مراقبت‌های بهداشتی | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | مردم‌شناسان و باستان‌شناسان | متخصصان منابع انسانی | متخصصان آموزش بهداشت</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Automated Neuropsychological Metric Assessments Battery | Behavioral Assessment and Research System BARS | BrainMetric The Category Test | BrainTrain Captain's Log | CogniSyst Computerized Assessment of Response Bias CARB | Conners' Continuous Performance Test II | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | IBM SPSS Statistics | نرم‌افزار ارزیابی روان‌شناختی تعاملی | MicroCog Assessment of Cognitive Functioning | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Noldus Information Technology The Observer XT | نرم‌افزار فروشگاه داده عملیاتی ODS | نرم‌افزار پرونده الکترونیک پزشکی بیمار EMR | نرم‌افزار آزمون روان‌شناختی | نرم‌افزار زمان‌بندی | نرم‌افزار آماری | The Tova Company Test of Variables of Attention | نرم‌افزار مرورگر وب</t>
+          <t>Automated Neuropsychological Metric Assessments Battery | Behavioral Assessment and Research System BARS | BrainMetric The Category Test | BrainTrain Captain's Log | CogniSyst Computerized Assessment of Response Bias CARB | Conners' Continuous Performance Test II | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | IBM SPSS Statistics | نرم‌افزار ارزیابی روان‌شناختی تعاملی | MicroCog Assessment of Cognitive Functioning | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Noldus Information Technology The Observer XT | نرم‌افزار ذخیره‌سازی داده‌های عملیاتی ODS | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار آزمون روان‌شناختی | نرم‌افزار زمان‌بندی | نرم‌افزار آماری | The Tova Company Test of Variables of Attention | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نوشتن | تفکر انتقادی | صحبت کردن | یادگیری فعال | نظارت | علم | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | جامعه‌شناسی و مردم‌شناسی | زیست‌شناسی | اداری | ریاضیات | کامپیوتر و الکترونیک</t>
+          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | جامعه‌شناسی و انسان‌شناسی | زیست‌شناسی | اداری | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان نوشتاری | درک شفاهی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | دید نزدیک | نظم‌دهی اطلاعات | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | ایمیل | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | بحث‌های حضوری با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | تکرار تصمیم‌گیری | تماس با دیگران | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | سطح رقابت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مجاورت فیزیکی | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | ایمیل | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | فراوانی تصمیم‌گیری | ارتباط با دیگران | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | سطح رقابت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران روان‌پزشکی پیشرفته | شنوایی‌شناسان | عصب‌روان‌شناسان بالینی | پرستاران بالینی متخصص | روان‌شناسان بالینی و مشاوره | پزشکان طب اورژانس | پزشکان طب خانواده | پزشکان داخلی عمومی | مشاوران ژنتیک | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | متخصصان مغز و اعصاب | پرستاران متخصص | کاردرمانگران | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توان‌بخشی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | روان‌شناسان مدرسه</t>
+          <t>پرستاران پیشرفته روانپزشکی | شنوایی‌شناسان | عصب‌روان‌شناسان بالینی | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | مشاوران ژنتیک | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | متخصصان مغز و اعصاب | پرستاران متخصص | کاردرمانگران | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | تکنسین‌های روانپزشکی | روان‌پزشکان | روان‌شناسان مدرسه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Automated Neuropsychological Metric Assessments Battery | Behavioral Assessment and Research System BARS | BrainMetric The Category Test | BrainTrain Captain's Log | CogniSyst Computerized Assessment of Response Bias CARB | Conners' Continuous Performance Test II | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | IBM SPSS Statistics | نرم‌افزار ارزیابی روان‌شناختی تعاملی | MicroCog Assessment of Cognitive Functioning | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Noldus Information Technology The Observer XT | نرم‌افزار پرونده الکترونیک پزشکی بیمار EMR | نرم‌افزار آزمون روان‌شناختی | نرم‌افزار زمان‌بندی | نرم‌افزار آماری | The Tova Company Test of Variables of Attention | نرم‌افزار مرورگر وب</t>
+          <t>Automated Neuropsychological Metric Assessments Battery | Behavioral Assessment and Research System BARS | BrainMetric The Category Test | BrainTrain Captain's Log | CogniSyst Computerized Assessment of Response Bias CARB | Conners' Continuous Performance Test II | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | IBM SPSS Statistics | نرم‌افزار ارزیابی روان‌شناختی تعاملی | MicroCog Assessment of Cognitive Functioning | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Noldus Information Technology The Observer XT | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار آزمون روان‌شناختی | نرم‌افزار زمان‌بندی | نرم‌افزار آماری | The Tova Company Test of Variables of Attention | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | صحبت کردن | نوشتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | ریاضیات | جامعه‌شناسی و مردم‌شناسی | کامپیوتر و الکترونیک</t>
+          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | ریاضیات | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان نوشتاری | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | نظم‌دهی اطلاعات | وضوح گفتار | دید نزدیک | انعطاف‌پذیری بستار | توجه انتخابی | روانی ایده‌ها | اصالت | دید دور | سرعت ادراکی | سرعت بستار | حافظه | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | ترتیب‌دهی اطلاعات | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری بستار | توجه انتخابی | روانی ایده‌ها | اصالت | بینایی دور | سرعت ادراکی | سرعت بستار | حفظ کردن | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تکرار تصمیم‌گیری | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مجاورت فیزیکی</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران روان‌پزشکی پیشرفته | متخصصان قلب | پرستاران بالینی متخصص | روان‌شناسان بالینی و مشاوره | پزشکان طب اورژانس | پزشکان طب خانواده | پزشکان داخلی عمومی | مشاوران ژنتیک | متخصصان مغز و اعصاب | عصب‌روان‌شناسان | پرستاران متخصص | کاردرمانگران | جراحان ارتوپد، به جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توان‌بخشی | دستیاران پزشک | تکنسین‌های روان‌پزشکی | روان‌پزشکان</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان قلب | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | مشاوران ژنتیک | متخصصان مغز و اعصاب | عصب‌روان‌شناسان | پرستاران متخصص | کاردرمانگران | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | تکنسین‌های روانپزشکی | روان‌پزشکان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ATLAS.ti | Adobe Acrobat | Adobe Dreamweaver | Adobe Photoshop | Circle Systems Stat/Transfer | نرم‌افزار تجسم داده | سیستم مدیریت پایگاه داده DBMS | نرم‌افزار ESRI ArcGIS | نرم‌افزار ایمیل | Facebook | نرم‌افزار حسابداری وجوه | Helios TextPad | IBM SPSS Statistics | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Visio | Microsoft Windows | Microsoft Word | Muthen &amp; Muthen Mplus | پایگاه‌های داده مرجع آنلاین | QSR International NVivo | Qualtrics Research Suite | R | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Scientific Software International HLM | Scientific Software International LISREL | سایت‌های رسانه‌های اجتماعی | StataCorp Stata | Thomson Reuters EndNote | VERBI MAXQDA | نرم‌افزار مرورگر وب | نرم‌افزار ویرایش وب</t>
+          <t>ATLAS.ti | Adobe Acrobat | Adobe Dreamweaver | Adobe Photoshop | Circle Systems Stat/Transfer | نرم‌افزار تجسم داده | سیستم مدیریت پایگاه داده DBMS | نرم‌افزار ESRI ArcGIS | نرم‌افزار ایمیل | Facebook | نرم‌افزار حسابداری صندوق | Helios TextPad | IBM SPSS Statistics | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Visio | Microsoft Windows | Microsoft Word | Muthen &amp; Muthen Mplus | پایگاه‌های داده مرجع آنلاین | QSR International NVivo | Qualtrics Research Suite | R | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Scientific Software International HLM | Scientific Software International LISREL | سایت‌های رسانه‌های اجتماعی | StataCorp Stata | Thomson Reuters EndNote | VERBI MAXQDA | نرم‌افزار مرورگر وب | نرم‌افزار ویرایش وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | نوشتن | درک مطلب | یادگیری فعال | تفکر انتقادی | راهبردهای یادگیری | نظارت | علم</t>
+          <t>سخن گفتن | گوش دادن فعال | نگارش | درک مطلب | یادگیری فعال | تفکر انتقادی | راهبردهای یادگیری | نظارت | علوم</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و مردم‌شناسی | زبان انگلیسی | آموزش و پرورش | ریاضیات | تاریخ و باستان‌شناسی | کامپیوتر و الکترونیک | قانون و دولت | روان‌شناسی | فلسفه و الهیات</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | آموزش و پرورش | ریاضیات | تاریخ و باستان‌شناسی | رایانه و الکترونیک | قانون و دولت | روان‌شناسی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | بیان نوشتاری | استدلال استقرایی | درک نوشتاری | استدلال قیاسی | وضوح گفتار | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | روانی ایده‌ها | نظم‌دهی اطلاعات | اصالت | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک شفاهی | بیان کتبی | استدلال استقرایی | درک کتبی | استدلال قیاسی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | روانی ایده‌ها | ترتیب‌دهی اطلاعات | اصالت | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های حضوری با افراد و درون تیم‌ها | صرف زمان برای نشستن | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | سطح رقابت | سخنرانی عمومی | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | تماس با دیگران</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | سطح رقابت | سخنرانی عمومی | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مردم‌شناسان و باستان‌شناسان | معلمان مردم‌شناسی و باستان‌شناسی، پس از متوسطه | معلمان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | عصب‌روان‌شناسان بالینی | دانشمندان داده | معلمان اقتصاد، پس از متوسطه | اقتصاددانان | معلمان آموزشی، پس از متوسطه | اپیدمیولوژیست‌ها | مورخان | روان‌شناسان صنعتی-سازمانی | عصب‌روان‌شناسان | معلمان علوم سیاسی، پس از متوسطه | دانشمندان علوم سیاسی | معلمان روان‌شناسی، پس از متوسطه | روان‌شناسان مدرسه | دستیاران پژوهشی علوم اجتماعی | معلمان مددکاری اجتماعی، پس از متوسطه | معلمان جامعه‌شناسی، پس از متوسطه | پژوهشگران نظرسنجی</t>
+          <t>مردم‌شناسان و باستان‌شناسان | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | عصب‌روان‌شناسان بالینی | دانشمندان داده | استادان اقتصاد، پس از متوسطه | اقتصاددانان | مدرسان علوم تربیتی، آموزش عالی | اپیدمیولوژیست‌ها | مورخان | روان‌شناسان صنعتی-سازمانی | عصب‌روان‌شناسان | استادان علوم سیاسی، پس از متوسطه | دانشمندان علوم سیاسی | استادان روان‌شناسی، پس از متوسطه | روان‌شناسان مدرسه | دستیاران تحقیقات علوم اجتماعی | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | پژوهشگران نظرسنجی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدل‌سازی شبیه‌سازی شهری سه‌بعدی | Accela KIVA DMS | Accela PERMITS Plus | Accela Tidemark Advantage | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe PageMaker | Adobe Photoshop | Autodesk 3ds Max Design | Autodesk AutoCAD | Autodesk AutoCAD Map 3D | Bentley MicroStation | Caliper TransCAD | Citilabs TRANPLAN | CommunityViz | Corel CorelDraw Graphics Suite | Corel WordPerfect Office Suite | Criterion Planners INDEX | Dassault Systemes SolidWorks | نرم‌افزار پایگاه داده | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | ESRI ArcView | ESRI What if? | نرم‌افزار ESRI | نرم‌افزار ایمیل | Esri ArcGIS | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار طراحی و تحلیل ژئومکانیکی GDA | نرم‌افزار گرافیکی | زبان نشانه‌گذاری ابرمتن HTML | IBM Lotus 1-2-3 | IBM Lotus Notes | ITC Integrated Land and Water Information System ILWIS | ITSpatial InterSCOPE | Intergraph MGE | نرم‌افزار Interwoven | پایگاه‌های داده مدیریت زمین | Leica Geosystems ERDAS IMAGINE | سیستم پشتیبانی تصمیم‌گیری تخصیص مکان LADSS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Word | MultiGen Paradigm 3D GIS | Oracle Database | Oracle Java | Oracle Primavera Systems | PlanGraphics Citywide GIS Utility | RhinoSoft FTP Voyager | RockWare ArcMap | نرم‌افزار SAP | Sage Timeslips | Scientific Software Group ModTech | ابزارهای توسعه نرم‌افزار | نرم‌افزار سیستم‌های پشتیبانی تصمیم‌گیری فضایی SDSS | پایگاه‌های داده آدرس خیابان | زبان پرس‌وجوی ساختاریافته SQL | Tangible Media Group Luminous Table | Telogis GeoBase | نرم‌افزار برنامه‌ریزی حمل‌ونقل | Trimble SketchUp Pro | UrbanSim | نرم‌افزار مرورگر وب | WorkTech MAXIMO | dBASE | e-on VUE</t>
+          <t>نرم‌افزار مدل‌سازی شبیه‌سازی شهری سه‌بعدی | Accela KIVA DMS | Accela PERMITS Plus | Accela Tidemark Advantage | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe PageMaker | Adobe Photoshop | Autodesk 3ds Max Design | Autodesk AutoCAD | Autodesk AutoCAD Map 3D | Bentley MicroStation | Caliper TransCAD | Citilabs TRANPLAN | CommunityViz | Corel CorelDraw Graphics Suite | Corel WordPerfect Office Suite | Criterion Planners INDEX | Dassault Systemes SolidWorks | نرم‌افزار پایگاه داده | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | ESRI ArcView | ESRI What if? | نرم‌افزار ESRI | نرم‌افزار ایمیل | Esri ArcGIS | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | نرم‌افزار گرافیکی | زبان نشانه‌گذاری ابرمتن HTML | IBM Lotus 1-2-3 | IBM Lotus Notes | ITC Integrated Land and Water Information System ILWIS | ITSpatial InterSCOPE | Intergraph MGE | Interwoven software | پایگاه‌های داده مدیریت زمین | Leica Geosystems ERDAS IMAGINE | سیستم پشتیبانی تصمیم‌گیری تخصیص مکان LADSS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Word | MultiGen Paradigm 3D GIS | Oracle Database | Oracle Java | Oracle Primavera Systems | PlanGraphics Citywide GIS Utility | RhinoSoft FTP Voyager | RockWare ArcMap | نرم‌افزار SAP | Sage Timeslips | Scientific Software Group ModTech | ابزارهای توسعه نرم‌افزار | نرم‌افزار سیستم‌های پشتیبانی تصمیم‌گیری فضایی SDSS | پایگاه‌های داده آدرس خیابان | زبان پرس‌وجوی ساختاریافته SQL | Tangible Media Group Luminous Table | Telogis GeoBase | نرم‌افزار برنامه‌ریزی حمل‌ونقل | Trimble SketchUp Pro | UrbanSim | نرم‌افزار مرورگر وب | WorkTech MAXIMO | dBASE | e-on VUE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | تفکر انتقادی | درک مطلب | نوشتن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>قانون و دولت | زبان انگلیسی | جغرافیا | حمل‌ونقل | ارتباطات و رسانه | مدیریت و اداره | جامعه‌شناسی و مردم‌شناسی | خدمات مشتری و شخصی | کامپیوتر و الکترونیک</t>
+          <t>قانون و دولت | زبان انگلیسی | جغرافیا | حمل و نقل | ارتباطات و رسانه | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | اصالت | تجسم | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی | دید دور</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | اصالت | تجسم | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی | بینایی دور</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | تماس با دیگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | فشار زمانی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | فشار زمانی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متخصصان بازسازی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد | مدیران ارشد پایداری | تحلیل‌گران سیاست تغییر اقلیم | دانشمندان حفاظت | مدیران مدیریت بحران | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست، شامل سلامت | جغرافیدانان | بازرسان و بازپرسان املاک دولتی | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | مدیران پروژه فناوری اطلاعات | معماران منظر | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | مدیران مرتع | متخصصان پایداری | برنامه‌ریزان حمل‌ونقل | متخصصان منابع آب</t>
+          <t>متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد اجرایی | مدیران ارشد پایداری | تحلیل‌گران سیاست تغییرات اقلیمی | دانشمندان حفاظت | مدیران مدیریت بحران | برنامه‌ریزان احیای محیط‌زیست | دانشمندان و متخصصان محیط زیست، شامل بهداشت | جغرافیدانان | بازرسان و محققان اموال دولتی | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | مدیران پروژه فناوری اطلاعات | معماران منظر | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | مدیران مراتع | متخصصان پایداری | برنامه‌ریزان حمل‌ونقل | متخصصان منابع آب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>صحبت کردن | نوشتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری | علم</t>
+          <t>سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و مردم‌شناسی | زبان انگلیسی | تاریخ و باستان‌شناسی | زبان خارجی | آموزش و پرورش | جغرافیا | ارتباطات و رسانه | فلسفه و الهیات | کامپیوتر و الکترونیک</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | تاریخ و باستان‌شناسی | زبان خارجی | آموزش و پرورش | جغرافیا | ارتباطات و رسانه | فلسفه و الهیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان نوشتاری | بیان شفاهی | درک نوشتاری | درک شفاهی | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | دید دور | توجه انتخابی | اصالت | تجسم</t>
+          <t>بیان کتبی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | بینایی دور | توجه انتخابی | اصالت | تجسم</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | بحث‌های حضوری با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | تماس با دیگران | صرف زمان برای نشستن | سطح رقابت | مکالمات تلفنی | محیط داخلی، دارای کنترل محیطی | فشار زمانی | سخنرانی عمومی</t>
+          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | صرف زمان برای نشستن | سطح رقابت | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | سخنرانی عمومی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>معلمان مردم‌شناسی و باستان‌شناسی، پس از متوسطه | بایگان‌ها | معلمان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | موزه‌داران | دانشمندان داده | معلمان زبان و ادبیات انگلیسی، پس از متوسطه | معلمان زبان و ادبیات خارجی، پس از متوسطه | جغرافیدانان | معلمان جغرافیا، پس از متوسطه | زمین‌شناسان، به جز هیدرولوژیست‌ها و جغرافیدانان | مورخان | معلمان تاریخ، پس از متوسطه | معلمان فلسفه و دین، پس از متوسطه | معلمان علوم سیاسی، پس از متوسطه | دانشمندان علوم سیاسی | دستیاران پژوهشی علوم اجتماعی | معلمان مددکاری اجتماعی، پس از متوسطه | جامعه‌شناسان | معلمان جامعه‌شناسی، پس از متوسطه | پژوهشگران نظرسنجی</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | آرشیوچی‌ها | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | موزه‌داران | دانشمندان داده | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | مدرسان زبان و ادبیات خارجی، آموزش عالی | جغرافیدانان | استادان جغرافیا، پس از متوسطه | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | مورخان | مدرسان تاریخ، آموزش عالی | اساتید فلسفه و دین، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | دانشمندان علوم سیاسی | دستیاران تحقیقات علوم اجتماعی | مدرسان مددکاری اجتماعی، آموزش عالی | جامعه‌شناسان | استادان جامعه‌شناسی، پس از متوسطه | پژوهشگران نظرسنجی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | نوشتن | تفکر انتقادی | صحبت کردن | گوش دادن فعال | یادگیری فعال | علم | راهبردهای یادگیری | نظارت | ریاضیات</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | علوم | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>جغرافیا | زبان انگلیسی | کامپیوتر و الکترونیک | آموزش و پرورش | جامعه‌شناسی و مردم‌شناسی | ریاضیات</t>
+          <t>جغرافیا | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان نوشتاری | استدلال استقرایی | درک شفاهی | بیان شفاهی | استدلال قیاسی | دید نزدیک | نظم‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار | اصالت | توانایی عددی | استدلال ریاضی | دید دور | تجسم</t>
+          <t>درک کتبی | بیان کتبی | استدلال استقرایی | درک شفاهی | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار | اصالت | توانایی عددی | استدلال ریاضی | بینایی دور | تجسم</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | صرف زمان برای نشستن | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | فشار زمانی</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | فشار زمانی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مردم‌شناسان و باستان‌شناسان | دانشمندان جوی و فضایی | نقشه‌برداران و فتوگرامتریست‌ها | دانشمندان حفاظت | دانشمندان داده | اقتصاددانان محیط زیست | نقشه‌برداران ژئودتیک | تکنسین‌ها و متخصصان فناوری سیستم‌های اطلاعات جغرافیایی | معلمان جغرافیا، پس از متوسطه | تکنسین‌های زمین‌شناسی، به جز تکنسین‌های هیدرولوژی | زمین‌شناسان، به جز هیدرولوژیست‌ها و جغرافیدانان | مورخان | تکنسین‌های هیدرولوژی | هیدرولوژیست‌ها | دانشمندان و متخصصان سنجش از دور | جامعه‌شناسان | آمارشناسان | پژوهشگران نظرسنجی | تکنسین‌های نقشه‌برداری و نقشه‌کشی | برنامه‌ریزان شهری و منطقه‌ای</t>
+          <t>مردم‌شناسان و باستان‌شناسان | دانشمندان علوم جوی و فضایی | نقشه‌برداران و فتوگرامتریست‌ها | دانشمندان حفاظت | دانشمندان داده | اقتصاددانان محیط‌زیست | نقشه‌برداران ژئودتیک | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | استادان جغرافیا، پس از متوسطه | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | مورخان | تکنسین‌های هیدرولوژی | آب‌شناسان | دانشمندان و فناوران سنجش از دور | جامعه‌شناسان | آمارشناسان | پژوهشگران نظرسنجی | تکنسین‌های نقشه‌برداری و نقشه‌کشی | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0025_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0025_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | علوم پایه | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | روان‌شناسی | آموزش و توانمندسازی | مدیریت و امور اداری | ریاضیات | زبان انگلیسی | خدمات مشتریان و خدمات فردی | امور حقوقی و دولتی | جامعه‌شناسی و مردم‌شناسی | رایانه و الکترونیک</t>
+          <t>پرسنل و منابع انسانی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره | ریاضیات | زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | روانی ایده‌ها | ابتکار | استدلال ریاضی | انعطاف‌پذیری در دسته‌بندی | دید نزدیک | توجه انتخابی | محاسبات عددی | دید دور</t>
+          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | توانایی عددی | بینایی دور</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>استادان علوم تجاری و بازرگانی در دانشگاه | روان‌شناسان بالینی و سلامت روان | دانشمندان داده | مدیران آموزشی دانشگاه‌ها و مؤسسات آموزش عالی | استادان علوم تربیتی در دانشگاه | مشاوران و راهنمایان تحصیلی و شغلی | کارشناسان امور دفتری منابع انسانی | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان هماهنگی برنامه‌های آموزشی | تحلیل‌گران فرایندهای مدیریتی | مدیران خدمات بهداشتی و درمانی | کارشناسان مدیریت پروژه | استادان روان‌شناسی در دانشگاه | مشاوران توانبخشی | روان‌شناسان مدارس | استادان مددکاری اجتماعی در دانشگاه | مدیران خدمات اجتماعی و رفاهی | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>استادان علوم اداری و مدیریت، آموزش عالی | روان‌شناسان بالینی و مشاوران سلامت روان | دانشمندان داده | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | کارشناسان مدیریت پروژه | استادان روان‌شناسی دانشگاه | مشاوران توانبخشی | روان‌شناسان مدارس | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | مدیران خدمات اجتماعی و خدمات مردمی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | آموزش و توانمندسازی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | درک شفاهی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | ابتکار | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | توجه انتخابی | دید نزدیک | انعطاف‌پذیری در نتیجه‌گیری شواهد</t>
+          <t>بیان شفاهی | درک کتبی | درک شفاهی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | توجه انتخابی | بینایی نزدیک | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی روان‌پزشکی | مددکاران اجتماعی کودک، خانواده و مدارس | متخصصان عصب‌روان‌شناسی بالینی | پرستاران بالینی متخصص | پزشکان عمومی و طب خانواده | مشاوران ژنتیک | مددکاران اجتماعی بخش سلامت و درمان | مشاوران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | متخصصان عصب‌روان‌شناسی | کاردرمانگران | بهیاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توانبخشی | روان‌شناسان مدارس | دستیاران خدمات اجتماعی و انسانی | مشاوران درمان سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>پرستاران تخصصی روانپزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان عصب‌روان‌شناسی بالینی | پرستاران متخصص بالینی | پزشکان عمومی و خانواده | مشاوران ژنتیک | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | متخصصان عصب‌روان‌شناسی | کاردرمانگران | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | روان‌شناسان مدارس | دستیاران خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | آموزش و توانمندسازی | جامعه‌شناسی و مردم‌شناسی | خدمات مشتریان و خدمات فردی | امور اداری و دفتری | ریاضیات | امور حقوقی و دولتی | رایانه و الکترونیک | زبان انگلیسی</t>
+          <t>روان‌شناسی | درمان و مشاوره | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | اداری | ریاضیات | قانون و دولت | رایانه و الکترونیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | وضوح گفتار | بیان کتبی | تشخیص گفتار | دید نزدیک | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | روانی ایده‌ها | ابتکار | توجه انتخابی | انعطاف‌پذیری در نتیجه‌گیری شواهد</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | وضوح گفتار | بیان کتبی | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدارس | متخصصان عصب‌روان‌شناسی بالینی | روان‌شناسان بالینی و سلامت روان | مدیران مدارس دوره‌های تحصیلی مختلف | استادان علوم تربیتی در دانشگاه | مشاوران و راهنمایان تحصیلی و شغلی | معلمان دوره ابتدایی (غیر از آموزش استثنایی) | مشاوران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | متخصصان عصب‌روان‌شناسی | روان‌پزشکان | استادان روان‌شناسی در دانشگاه | مشاوران توانبخشی | استادان مددکاری اجتماعی در دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | مربیان آموزش استثنایی پیش‌دبستانی | معلمان آموزش استثنایی دوره متوسطه اول | معلمان آموزش استثنایی دوره متوسطه دوم | آموزگاران و مدرسان خصوصی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان عصب‌روان‌شناسی بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | متخصصان عصب‌روان‌شناسی | روان‌پزشکان | استادان روان‌شناسی دانشگاه | مشاوران توانبخشی | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>روان‌شناسی | زبان انگلیسی | درمان و مشاوره | جامعه‌شناسی و مردم‌شناسی | آموزش و توانمندسازی | ریاضیات | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>روان‌شناسی | زبان انگلیسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | ریاضیات | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | روانی ایده‌ها | ابتکار | توجه انتخابی | تقسیم زمان بین چند فعالیت | تصویرسازی ذهنی | حافظه و یادآوری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>روان‌شناسان بالینی و سلامت روان | روان‌شناسان مدارس | روان‌شناسان صنعتی و سازمانی | متخصصان عصب‌روان‌شناسی | متخصصان عصب‌روان‌شناسی بالینی | مشاوران ازدواج و خانواده | مشاوران سلامت روان | مشاوران درمان سوءمصرف مواد و اختلالات رفتاری | مشاوران توانبخشی | مشاوران و راهنمایان تحصیلی و شغلی | جامعه‌شناسان | پژوهشگران نظرسنجی و پیمایش | دستیاران پژوهشی علوم اجتماعی | استادان روان‌شناسی در دانشگاه | مددکاران اجتماعی بخش سلامت و درمان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | دانشمندان علوم پزشکی (به‌جز همه‌گیرشناسان) | انسان‌شناسان و باستان‌شناسان | کارشناسان منابع انسانی | کارشناسان آموزش و ارتقای سلامت</t>
+          <t>روان‌شناسان بالینی و مشاوران سلامت روان | روان‌شناسان مدارس | روان‌شناسان صنعتی و سازمانی | متخصصان عصب‌روان‌شناسی | متخصصان عصب‌روان‌شناسی بالینی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران اعتیاد و اختلالات رفتاری | مشاوران توانبخشی | مشاوران تحصیلی، شغلی و هدایت استعدادها | جامعه‌شناسان | پژوهشگران پیمایشی و افکارسنجی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | استادان روان‌شناسی دانشگاه | مددکاران اجتماعی بخش سلامت و درمان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | پژوهشگران و دانشمندان علوم پزشکی | انسان‌شناسان و باستان‌شناسان | کارشناسان منابع انسانی | کارشناسان آموزش بهداشت و ارتقای سلامت</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت | علوم پایه | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و توانمندسازی | خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | جامعه‌شناسی و مردم‌شناسی | زیست‌شناسی | امور اداری و دفتری | ریاضیات | رایانه و الکترونیک</t>
+          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | جامعه‌شناسی و انسان‌شناسی | زیست‌شناسی | اداری | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | دید نزدیک | مرتب‌سازی اطلاعات | روانی ایده‌ها | ابتکار | توجه انتخابی | انعطاف‌پذیری در نتیجه‌گیری شواهد | استدلال ریاضی</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی روان‌پزشکی | شنوایی‌شناسان | متخصصان عصب‌روان‌شناسی بالینی | پرستاران بالینی متخصص | روان‌شناسان بالینی و سلامت روان | پزشکان طب اورژانس | پزشکان عمومی و طب خانواده | متخصصان داخلی عمومی | مشاوران ژنتیک | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | متخصصان بیماری‌های مغز و اعصاب (نورولوژیست‌ها) | پرستاران دارای پروانه طبابت پیشرفته | کاردرمانگران | جراحان اطفال | پزشکان متخصص کودکان (اطفال عمومی) | متخصصان طب فیزیکی و توانبخشی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | روان‌شناسان مدارس</t>
+          <t>پرستاران تخصصی روانپزشکی | شنوایی‌شناسان | متخصصان عصب‌روان‌شناسی بالینی | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | مشاوران ژنتیک | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | کاردرمانگران | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | روان‌شناسان مدارس</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و توانمندسازی | پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | ریاضیات | جامعه‌شناسی و مردم‌شناسی | رایانه و الکترونیک</t>
+          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | ریاضیات | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | انعطاف‌پذیری در دسته‌بندی | تشخیص گفتار | مرتب‌سازی اطلاعات | وضوح گفتار | دید نزدیک | انعطاف‌پذیری در نتیجه‌گیری شواهد | توجه انتخابی | روانی ایده‌ها | ابتکار | دید دور | سرعت ادراک | سرعت در نتیجه‌گیری شواهد | حافظه و یادآوری | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | ترتیب‌دهی اطلاعات | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری بستار | توجه انتخابی | روانی ایده‌ها | اصالت | بینایی دور | سرعت ادراکی | سرعت بستار | حفظ کردن | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های ویژه | پرستاران تخصصی روان‌پزشکی | متخصصان قلب و عروق | پرستاران بالینی متخصص | روان‌شناسان بالینی و سلامت روان | پزشکان طب اورژانس | پزشکان عمومی و طب خانواده | متخصصان داخلی عمومی | مشاوران ژنتیک | متخصصان بیماری‌های مغز و اعصاب (نورولوژیست‌ها) | متخصصان عصب‌روان‌شناسی | پرستاران دارای پروانه طبابت پیشرفته | کاردرمانگران | جراحان ارتوپدی (غیر از اطفال) | جراحان اطفال | پزشکان متخصص کودکان (اطفال عمومی) | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | تکنسین‌های روان‌پزشکی | روان‌پزشکان</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | مشاوران ژنتیک | متخصصان مغز و اعصاب | متخصصان عصب‌روان‌شناسی | پرستاران بالینی پیشرفته | کاردرمانگران | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نگارش | درک مطلب | یادگیری فعال | تفکر انتقادی | استراتژی‌های یادگیری | نظارت | علوم پایه</t>
+          <t>سخن گفتن | گوش دادن فعال | نگارش | درک مطلب | یادگیری فعال | تفکر انتقادی | راهبردهای یادگیری | نظارت | علوم</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و مردم‌شناسی | زبان انگلیسی | آموزش و توانمندسازی | ریاضیات | تاریخ و باستان‌شناسی | رایانه و الکترونیک | امور حقوقی و دولتی | روان‌شناسی | فلسفه و الهیات</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | آموزش و پرورش | ریاضیات | تاریخ و باستان‌شناسی | رایانه و الکترونیک | قانون و دولت | روان‌شناسی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | بیان کتبی | استدلال استقرایی | درک کتبی | استدلال قیاسی | وضوح گفتار | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | حساسیت به مسئله | روانی ایده‌ها | مرتب‌سازی اطلاعات | ابتکار | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک شفاهی | بیان کتبی | استدلال استقرایی | درک کتبی | استدلال قیاسی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | روانی ایده‌ها | ترتیب‌دهی اطلاعات | اصالت | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>انسان‌شناسان و باستان‌شناسان | استادان انسان‌شناسی و باستان‌شناسی در دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی در دانشگاه | متخصصان عصب‌روان‌شناسی بالینی | دانشمندان داده | استادان اقتصاد در دانشگاه | اقتصاددانان | استادان علوم تربیتی در دانشگاه | متخصصان اپیدمیولوژی (همه‌گیرشناسان) | تاریخ‌نگاران | روان‌شناسان صنعتی و سازمانی | متخصصان عصب‌روان‌شناسی | استادان علوم سیاسی در دانشگاه | دانشمندان علوم سیاسی | استادان روان‌شناسی در دانشگاه | روان‌شناسان مدارس | دستیاران پژوهشی علوم اجتماعی | استادان مددکاری اجتماعی در دانشگاه | استادان جامعه‌شناسی در دانشگاه | پژوهشگران نظرسنجی و پیمایش</t>
+          <t>انسان‌شناسان و باستان‌شناسان | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | متخصصان عصب‌روان‌شناسی بالینی | دانشمندان داده | استادان اقتصاد دانشگاه | اقتصاددانان | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | مورخان | روان‌شناسان صنعتی و سازمانی | متخصصان عصب‌روان‌شناسی | استادان علوم سیاسی دانشگاه | دانشمندان و پژوهشگران علوم سیاسی | استادان روان‌شناسی دانشگاه | روان‌شناسان مدارس | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | پژوهشگران پیمایشی و افکارسنجی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>امور حقوقی و دولتی | زبان انگلیسی | جغرافیا | ترابری و حمل‌ونقل | ارتباطات و رسانه | مدیریت و امور اداری | جامعه‌شناسی و مردم‌شناسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک</t>
+          <t>قانون و دولت | زبان انگلیسی | جغرافیا | حمل و نقل | ارتباطات و رسانه | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | ابتکار | تصویرسازی ذهنی | استدلال ریاضی | انعطاف‌پذیری در نتیجه‌گیری شواهد | محاسبات عددی | دید دور</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | اصالت | تجسم | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی | بینایی دور</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان احیای اراضی قهوه‌ای و مدیران سایت | مدیران ارشد اجرایی | مدیران ارشد پایداری | تحلیل‌گران سیاست‌گذاری تغییرات اقلیمی | دانشمندان علوم حفاظت از منابع طبیعی | مدیران مدیریت بحران و شرایط اضطراری | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست (شامل بهداشت محیط) | جغرافیدانان | بازرسان و ممیزان املاک دولتی | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | مدیران پروژه‌های فناوری اطلاعات | معماران منظر | تحلیل‌گران فرایندهای مدیریتی | کارشناسان مدیریت پروژه | کارشناسان مدیریت مرتع | متخصصان پایداری زیست‌محیطی | برنامه‌ریزان سیستم‌های حمل‌ونقل | کارشناسان منابع آب</t>
+          <t>مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مدیران عامل و مدیران ارشد اجرایی | مدیران ارشد پایداری سازمانی | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | مدیران مدیریت بحران و پدافند غیرعامل | برنامه‌ریزان احیای محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | جغرافیدانان | بازرسان و ممیزان اموال دولتی | تکنسین‌های آب‌شناسی و هیدرولوژی | بوم‌شناسان صنعتی | مدیران پروژه‌های فناوری اطلاعات | مهندسان معمار منظر | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت پروژه | مدیران و کارشناسان مدیریت مراتع | کارشناسان پایداری و توسعه پایدار | برنامه‌ریزان سیستم‌های حمل‌ونقل | کارشناسان و متخصصان مدیریت منابع آب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | درک مطلب | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و مردم‌شناسی | زبان انگلیسی | تاریخ و باستان‌شناسی | زبان‌های خارجی | آموزش و توانمندسازی | جغرافیا | ارتباطات و رسانه | فلسفه و الهیات | رایانه و الکترونیک</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | تاریخ و باستان‌شناسی | زبان خارجی | آموزش و پرورش | جغرافیا | ارتباطات و رسانه | فلسفه و الهیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان کتبی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری در نتیجه‌گیری شواهد | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | دید دور | توجه انتخابی | ابتکار | تصویرسازی ذهنی</t>
+          <t>بیان کتبی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | بینایی دور | توجه انتخابی | اصالت | تجسم</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>استادان انسان‌شناسی و باستان‌شناسی در دانشگاه | کارشناسان اسناد و مدارک تاریخی و آرشیوداران | استادان مطالعات منطقه‌ای، قومی و فرهنگی در دانشگاه | موزه‌داران | دانشمندان داده | استادان زبان و ادبیات انگلیسی در دانشگاه | استادان زبان‌ها و ادبیات خارجی در دانشگاه | جغرافیدانان | استادان جغرافیا در دانشگاه | دانشمندان علوم زمین (به‌جز هیدرولوژیست‌ها و جغرافیدانان) | تاریخ‌نگاران | استادان تاریخ در دانشگاه | استادان فلسفه و الهیات در دانشگاه | استادان علوم سیاسی در دانشگاه | دانشمندان علوم سیاسی | دستیاران پژوهشی علوم اجتماعی | استادان مددکاری اجتماعی در دانشگاه | جامعه‌شناسان | استادان جامعه‌شناسی در دانشگاه | پژوهشگران نظرسنجی و پیمایش</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | کارشناسان اسناد و آرشیو | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | موزه‌داران | دانشمندان داده | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات خارجی در دانشگاه‌ها و مراکز آموزش عالی | جغرافیدانان | استادان جغرافیای دانشگاه | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | مورخان | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان فلسفه و الهیات در آموزش عالی | استادان علوم سیاسی دانشگاه | دانشمندان و پژوهشگران علوم سیاسی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | جامعه‌شناسان | استادان جامعه‌شناسی دانشگاه | پژوهشگران پیمایشی و افکارسنجی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | شنیدن فعال | یادگیری فعال | علوم پایه | استراتژی‌های یادگیری | نظارت | ریاضیات</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | علوم | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>جغرافیا | زبان انگلیسی | رایانه و الکترونیک | آموزش و توانمندسازی | جامعه‌شناسی و مردم‌شناسی | ریاضیات</t>
+          <t>جغرافیا | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | استدلال استقرایی | درک شفاهی | بیان شفاهی | استدلال قیاسی | دید نزدیک | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری در دسته‌بندی | روانی ایده‌ها | سرعت ادراک | انعطاف‌پذیری در نتیجه‌گیری شواهد | ابتکار | محاسبات عددی | استدلال ریاضی | دید دور | تصویرسازی ذهنی</t>
+          <t>درک کتبی | بیان کتبی | استدلال استقرایی | درک شفاهی | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار | اصالت | توانایی عددی | استدلال ریاضی | بینایی دور | تجسم</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>انسان‌شناسان و باستان‌شناسان | دانشمندان علوم جوی و فضا | نقشه‌نگاران و متخصصان فتوگرامتری | دانشمندان علوم حفاظت از منابع طبیعی | دانشمندان داده | اقتصاددانان محیط زیست | نقشه‌برداران ژئودتیک | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی GIS | استادان جغرافیا در دانشگاه | تکنسین‌های زمین‌شناسی (غیر از هیدرولوژی) | دانشمندان علوم زمین (به‌جز هیدرولوژیست‌ها و جغرافیدانان) | تاریخ‌نگاران | تکنسین‌های هیدرولوژی | هیدرولوژیست‌ها (آب‌شناسان) | متخصصان و دانشمندان سنجش از دور | جامعه‌شناسان | آمارشناسان | پژوهشگران نظرسنجی و پیمایش | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | برنامه‌ریزان شهری و منطقه‌ای</t>
+          <t>انسان‌شناسان و باستان‌شناسان | دانشمندان و کارشناسان علوم جوی و فضا | کارشناسان نقشه‌نگاری و فتوگرامتری | دانشمندان حفاظت از منابع طبیعی | دانشمندان داده | اقتصاددانان محیط زیست | مهندسان نقشه‌برداری ژئودزی | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | استادان جغرافیای دانشگاه | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | مورخان | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | دانشمندان و فناوران سنجش از دور | جامعه‌شناسان | کارشناسان آمار | پژوهشگران پیمایشی و افکارسنجی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
